--- a/data/trans_dic/P44A$sangre-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P44A$sangre-Provincia-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han realizado al menos una prueba de sangre oculta en heces para detectar cáncer de colon</t>
+          <t>Población a la que le han realizado al menos una prueba de sangre oculta en heces para detectar cáncer de colon (tasa de respuesta: 98,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 8,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>55,6; 75,49</t>
+          <t>56,36; 75,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,29</t>
+          <t>0,0; 28,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,21; 85,74</t>
+          <t>67,23; 86,41</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,16</t>
+          <t>0,0; 12,05</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>62,78; 77,12</t>
+          <t>62,71; 76,82</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,53</t>
+          <t>0,0; 29,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,02</t>
+          <t>0,0; 42,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>68,93; 88,85</t>
+          <t>68,4; 89,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 9,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 74,6</t>
+          <t>0,0; 79,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>75,37; 92,28</t>
+          <t>74,99; 92,37</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,4</t>
+          <t>0,0; 15,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,73</t>
+          <t>0,0; 39,45</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>73,58; 88,2</t>
+          <t>73,5; 88,2</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 62,33</t>
+          <t>0,0; 62,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,28; 47,41</t>
+          <t>9,05; 44,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>51,12; 72,13</t>
+          <t>51,55; 73,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,28</t>
+          <t>0,0; 47,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,76</t>
+          <t>0,0; 23,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>65,46; 82,5</t>
+          <t>66,56; 82,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,36; 39,12</t>
+          <t>4,17; 37,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,38; 27,26</t>
+          <t>6,61; 29,22</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>62,49; 75,44</t>
+          <t>62,31; 75,49</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,65</t>
+          <t>0,0; 28,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>50,28; 74,53</t>
+          <t>49,76; 72,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,49</t>
+          <t>0,0; 43,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,57</t>
+          <t>0,0; 24,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>41,43; 60,67</t>
+          <t>41,36; 58,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,21</t>
+          <t>0,0; 24,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,56</t>
+          <t>0,0; 17,01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>48,27; 63,72</t>
+          <t>48,04; 63,13</t>
         </is>
       </c>
     </row>
@@ -1118,22 +1118,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,71; 53,24</t>
+          <t>15,7; 52,47</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 67,5</t>
+          <t>0,0; 67,51</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1143,22 +1143,22 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,32; 71,19</t>
+          <t>39,18; 71,81</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,85</t>
+          <t>0,0; 42,25</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,9</t>
+          <t>0,0; 57,43</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>32,5; 57,51</t>
+          <t>31,9; 57,07</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10,96; 67,42</t>
+          <t>11,02; 67,59</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>47,39; 70,59</t>
+          <t>46,62; 70,7</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>69,08; 89,95</t>
+          <t>68,76; 89,25</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,54; 46,7</t>
+          <t>6,56; 46,69</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>60,05; 76,59</t>
+          <t>60,06; 76,37</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,75; 47,0</t>
+          <t>5,47; 46,99</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,02; 34,35</t>
+          <t>9,73; 36,13</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>35,31; 52,56</t>
+          <t>34,39; 52,55</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,95</t>
+          <t>0,0; 33,7</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,76; 34,66</t>
+          <t>3,87; 33,74</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>58,69; 72,35</t>
+          <t>57,13; 72,24</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,45; 28,88</t>
+          <t>5,41; 28,45</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9,83; 28,5</t>
+          <t>9,13; 28,56</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>49,17; 60,83</t>
+          <t>49,54; 60,84</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>16,9; 58,45</t>
+          <t>16,34; 58,98</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,58</t>
+          <t>0,0; 29,45</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>78,06; 98,26</t>
+          <t>77,27; 98,09</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,24</t>
+          <t>0,0; 41,51</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>69,27; 80,45</t>
+          <t>69,78; 81,0</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,79; 43,15</t>
+          <t>14,88; 43,25</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,74</t>
+          <t>0,0; 16,15</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>76,75; 96,19</t>
+          <t>76,65; 96,75</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>11,08; 28,27</t>
+          <t>11,18; 27,2</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6,76; 16,74</t>
+          <t>6,56; 16,89</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>63,62; 89,68</t>
+          <t>63,29; 90,1</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,21; 15,61</t>
+          <t>3,86; 15,6</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,8; 14,01</t>
+          <t>3,62; 13,77</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>67,69; 73,86</t>
+          <t>67,7; 73,62</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,22; 19,08</t>
+          <t>9,16; 18,79</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6,46; 13,74</t>
+          <t>6,41; 13,95</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>66,75; 85,69</t>
+          <t>67,02; 86,69</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han realizado al menos una prueba de sangre oculta en heces para detectar cáncer de colon</t>
+          <t>Población a la que le han realizado al menos una prueba de sangre oculta en heces para detectar cáncer de colon (tasa de respuesta: 98,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1617</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 1933</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>40794; 55384</t>
+          <t>41346; 55275</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 1890</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4309</t>
+          <t>0; 4476</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23255; 30117</t>
+          <t>23613; 30353</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 1899</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 5153</t>
+          <t>0; 4717</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>68116; 83670</t>
+          <t>68033; 83345</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 6398</t>
+          <t>0; 7223</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4755</t>
+          <t>0; 3942</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>43069; 55516</t>
+          <t>42736; 55665</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 1938</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4255</t>
+          <t>0; 4550</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>29785; 36468</t>
+          <t>29635; 36503</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 6414</t>
+          <t>0; 6682</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 5519</t>
+          <t>0; 5926</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>75048; 89959</t>
+          <t>74965; 89958</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5746</t>
+          <t>0; 5775</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1937; 9902</t>
+          <t>1890; 9202</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>29037; 40968</t>
+          <t>29283; 41541</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 5362</t>
+          <t>0; 6305</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5539</t>
+          <t>0; 4679</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>36498; 45997</t>
+          <t>37112; 46061</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>983; 8814</t>
+          <t>940; 8487</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2607; 11135</t>
+          <t>2701; 11934</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>70333; 84913</t>
+          <t>70134; 84968</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 2046</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 6675</t>
+          <t>0; 7358</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26505; 39282</t>
+          <t>26225; 38256</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 5950</t>
+          <t>0; 5975</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 6038</t>
+          <t>0; 5015</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24450; 35807</t>
+          <t>24411; 34655</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 6693</t>
+          <t>0; 6063</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 8619</t>
+          <t>0; 7902</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>53933; 71193</t>
+          <t>53678; 70536</t>
         </is>
       </c>
     </row>
@@ -2513,22 +2513,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 1664</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 1320</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2023; 6854</t>
+          <t>2022; 6755</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 4432</t>
+          <t>0; 4433</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2538,22 +2538,22 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5341; 9922</t>
+          <t>5460; 10008</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 4483</t>
+          <t>0; 5435</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 3960</t>
+          <t>0; 3998</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8713; 15417</t>
+          <t>8553; 15302</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1014; 6235</t>
+          <t>1019; 6251</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 1774</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>18453; 27484</t>
+          <t>18150; 27527</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 1662</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 1786</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>21107; 27482</t>
+          <t>21009; 27267</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1017; 7258</t>
+          <t>1019; 7256</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 1897</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>41729; 53217</t>
+          <t>41733; 53065</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>903; 7381</t>
+          <t>859; 7380</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3638; 13848</t>
+          <t>3923; 14568</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>37294; 55513</t>
+          <t>36322; 55497</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 6367</t>
+          <t>0; 6933</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1059; 9773</t>
+          <t>1091; 9514</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>66963; 82549</t>
+          <t>65191; 82426</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1977; 10477</t>
+          <t>1962; 10322</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>6734; 19530</t>
+          <t>6259; 19572</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>108030; 133653</t>
+          <t>108856; 133672</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>4546; 15729</t>
+          <t>4396; 15872</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 7020</t>
+          <t>0; 7778</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>291917; 367449</t>
+          <t>288940; 366806</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0; 5301</t>
+          <t>0; 6245</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 1954</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>90124; 104677</t>
+          <t>90785; 105387</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>6204; 18102</t>
+          <t>6242; 18147</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0; 7870</t>
+          <t>0; 6442</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>386855; 484839</t>
+          <t>386376; 487695</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>12122; 30912</t>
+          <t>12226; 29752</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>10801; 26726</t>
+          <t>10482; 26977</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>494134; 696550</t>
+          <t>491588; 699871</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4504; 16699</t>
+          <t>4125; 16680</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>4410; 16270</t>
+          <t>4200; 15993</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>323638; 353144</t>
+          <t>323663; 351987</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>19953; 41268</t>
+          <t>19817; 40649</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>17810; 37903</t>
+          <t>17675; 38486</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>837575; 1075311</t>
+          <t>840970; 1087759</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P44A$sangre-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P44A$sangre-Provincia-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>64,54%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>77,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>68,77%</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>56,36; 75,34</t>
+          <t>54,39; 73,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -698,12 +698,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,35</t>
+          <t>0,0; 29,26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>67,23; 86,41</t>
+          <t>66,93; 85,71</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,05</t>
+          <t>0,0; 11,19</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>62,71; 76,82</t>
+          <t>60,85; 75,65</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>81,15%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>82,79%</t>
         </is>
       </c>
     </row>
@@ -788,17 +788,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,96</t>
+          <t>0,0; 29,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,3</t>
+          <t>0,0; 42,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>68,4; 89,09</t>
+          <t>70,3; 89,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -808,27 +808,27 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 79,77</t>
+          <t>0,0; 77,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>74,99; 92,37</t>
+          <t>76,29; 92,69</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,01</t>
+          <t>0,0; 16,5</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,45</t>
+          <t>0,0; 38,63</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>73,5; 88,2</t>
+          <t>75,12; 88,76</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>63,43%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>74,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>69,01%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 62,64</t>
+          <t>0,0; 58,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,05; 44,06</t>
+          <t>9,32; 47,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>51,55; 73,14</t>
+          <t>52,89; 73,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,36</t>
+          <t>0,0; 39,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,45</t>
+          <t>0,0; 21,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>66,56; 82,62</t>
+          <t>65,14; 82,46</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,17; 37,67</t>
+          <t>4,53; 39,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,61; 29,22</t>
+          <t>4,85; 28,23</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>62,31; 75,49</t>
+          <t>61,56; 75,51</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>59,76%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>50,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>55,15%</t>
         </is>
       </c>
     </row>
@@ -1013,42 +1013,42 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,27</t>
+          <t>0,0; 35,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>49,76; 72,58</t>
+          <t>47,8; 71,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,67</t>
+          <t>0,0; 37,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,56</t>
+          <t>0,0; 28,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>41,36; 58,72</t>
+          <t>41,54; 59,96</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,65</t>
+          <t>0,0; 22,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,01</t>
+          <t>0,0; 18,81</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>48,04; 63,13</t>
+          <t>47,86; 62,53</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>56,33%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>45,06%</t>
         </is>
       </c>
     </row>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,7; 52,47</t>
+          <t>15,49; 53,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 67,51</t>
+          <t>0,0; 67,5</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1143,22 +1143,22 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>39,18; 71,81</t>
+          <t>40,04; 71,3</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,25</t>
+          <t>0,0; 34,7</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,43</t>
+          <t>0,0; 57,46</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>31,9; 57,07</t>
+          <t>33,54; 56,97</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>59,38%</t>
+          <t>59,33%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>80,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>69,05%</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11,02; 67,59</t>
+          <t>11,04; 68,37</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>46,62; 70,7</t>
+          <t>47,08; 71,04</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>68,76; 89,25</t>
+          <t>68,98; 89,07</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,56; 46,69</t>
+          <t>6,59; 46,34</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>60,06; 76,37</t>
+          <t>59,86; 76,67</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>65,46%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>55,09%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,47; 46,99</t>
+          <t>5,44; 48,3</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,73; 36,13</t>
+          <t>9,95; 35,46</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>34,39; 52,55</t>
+          <t>35,64; 52,46</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,7</t>
+          <t>0,0; 35,1</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,87; 33,74</t>
+          <t>3,93; 34,66</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>57,13; 72,24</t>
+          <t>58,75; 72,37</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,41; 28,45</t>
+          <t>5,45; 28,19</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9,13; 28,56</t>
+          <t>9,97; 29,46</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>49,54; 60,84</t>
+          <t>49,65; 60,89</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>79,98%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>75,57%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>77,74%</t>
         </is>
       </c>
     </row>
@@ -1448,22 +1448,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>16,34; 58,98</t>
+          <t>16,5; 58,68</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,45</t>
+          <t>0,0; 30,02</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>77,27; 98,09</t>
+          <t>73,11; 85,41</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,51</t>
+          <t>0,0; 42,27</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1473,22 +1473,22 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>69,78; 81,0</t>
+          <t>70,06; 81,08</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,88; 43,25</t>
+          <t>14,59; 44,85</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,15</t>
+          <t>0,0; 22,99</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>76,65; 96,75</t>
+          <t>73,55; 81,58</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>64,15%</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>70,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>67,25%</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>11,18; 27,2</t>
+          <t>11,44; 28,04</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6,56; 16,89</t>
+          <t>6,16; 16,26</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>63,29; 90,1</t>
+          <t>60,42; 68,1</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,86; 15,6</t>
+          <t>4,09; 15,06</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,62; 13,77</t>
+          <t>3,84; 15,14</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>67,7; 73,62</t>
+          <t>67,39; 73,48</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,16; 18,79</t>
+          <t>9,05; 19,45</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6,41; 13,95</t>
+          <t>6,64; 14,0</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>67,02; 86,69</t>
+          <t>64,9; 69,48</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48761</t>
+          <t>47463</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27399</t>
+          <t>27973</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>76160</t>
+          <t>75436</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>41346; 55275</t>
+          <t>39996; 53791</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4476</t>
+          <t>0; 4618</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23613; 30353</t>
+          <t>24201; 30990</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4717</t>
+          <t>0; 4382</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>68033; 83345</t>
+          <t>66755; 82981</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>50231</t>
+          <t>52779</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>33456</t>
+          <t>35983</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>83686</t>
+          <t>88762</t>
         </is>
       </c>
     </row>
@@ -2024,17 +2024,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 7223</t>
+          <t>0; 7148</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3942</t>
+          <t>0; 3999</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>42736; 55665</t>
+          <t>45722; 58137</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2044,27 +2044,27 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4550</t>
+          <t>0; 4398</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>29635; 36503</t>
+          <t>32177; 39094</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 6682</t>
+          <t>0; 7349</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 5926</t>
+          <t>0; 5803</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>74965; 89958</t>
+          <t>80543; 95164</t>
         </is>
       </c>
     </row>
@@ -2144,7 +2144,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35908</t>
+          <t>35294</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>41747</t>
+          <t>42575</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>77657</t>
+          <t>77869</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5775</t>
+          <t>0; 5357</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1890; 9202</t>
+          <t>1948; 9866</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>29283; 41541</t>
+          <t>29429; 40821</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 6305</t>
+          <t>0; 5317</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4679</t>
+          <t>0; 4359</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>37112; 46061</t>
+          <t>37259; 47171</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>940; 8487</t>
+          <t>1020; 8830</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2701; 11934</t>
+          <t>1980; 11529</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>70134; 84968</t>
+          <t>69466; 85205</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>32682</t>
+          <t>35407</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>29844</t>
+          <t>32369</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>62526</t>
+          <t>67776</t>
         </is>
       </c>
     </row>
@@ -2355,42 +2355,42 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 7358</t>
+          <t>0; 9231</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26225; 38256</t>
+          <t>28321; 42550</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 5975</t>
+          <t>0; 5187</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 5015</t>
+          <t>0; 5759</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24411; 34655</t>
+          <t>26436; 38157</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 6063</t>
+          <t>0; 5556</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 7902</t>
+          <t>0; 8739</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>53678; 70536</t>
+          <t>58816; 76841</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4186</t>
+          <t>4429</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7776</t>
+          <t>8306</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>11962</t>
+          <t>12735</t>
         </is>
       </c>
     </row>
@@ -2523,12 +2523,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2022; 6755</t>
+          <t>2094; 7236</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 4433</t>
+          <t>0; 4432</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2538,22 +2538,22 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5460; 10008</t>
+          <t>5904; 10513</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 5435</t>
+          <t>0; 4464</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 3998</t>
+          <t>0; 4000</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8553; 15302</t>
+          <t>9479; 16103</t>
         </is>
       </c>
     </row>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>23120</t>
+          <t>22450</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24656</t>
+          <t>25103</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>47775</t>
+          <t>47553</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1019; 6251</t>
+          <t>1021; 6323</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>18150; 27527</t>
+          <t>17815; 26879</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>21009; 27267</t>
+          <t>21403; 27638</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1019; 7256</t>
+          <t>1025; 7202</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>41733; 53065</t>
+          <t>41225; 52797</t>
         </is>
       </c>
     </row>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>46271</t>
+          <t>52865</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>74693</t>
+          <t>88328</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>120965</t>
+          <t>141192</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>859; 7380</t>
+          <t>855; 7586</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3923; 14568</t>
+          <t>4012; 14298</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>36322; 55497</t>
+          <t>43323; 63766</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 6933</t>
+          <t>0; 7221</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1091; 9514</t>
+          <t>1108; 9772</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>65191; 82426</t>
+          <t>79161; 97521</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1962; 10322</t>
+          <t>1979; 10225</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>6259; 19572</t>
+          <t>6830; 20184</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>108856; 133672</t>
+          <t>127249; 156058</t>
         </is>
       </c>
     </row>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>347886</t>
+          <t>115554</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98435</t>
+          <t>112265</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>446321</t>
+          <t>227820</t>
         </is>
       </c>
     </row>
@@ -3002,22 +3002,22 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>4396; 15872</t>
+          <t>4440; 15789</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 7778</t>
+          <t>0; 7927</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>288940; 366806</t>
+          <t>105635; 123408</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0; 6245</t>
+          <t>0; 6360</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3027,22 +3027,22 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>90785; 105387</t>
+          <t>104079; 120454</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>6242; 18147</t>
+          <t>6123; 18815</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0; 6442</t>
+          <t>0; 9166</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>386376; 487695</t>
+          <t>215550; 239072</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>589045</t>
+          <t>366242</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>338007</t>
+          <t>372902</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>927052</t>
+          <t>739144</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>12226; 29752</t>
+          <t>12508; 30662</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>10482; 26977</t>
+          <t>9844; 25970</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>491588; 699871</t>
+          <t>344945; 388744</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4125; 16680</t>
+          <t>4369; 16111</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>4200; 15993</t>
+          <t>4458; 17587</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>323663; 351987</t>
+          <t>356019; 388187</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>19817; 40649</t>
+          <t>19570; 42080</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>17675; 38486</t>
+          <t>18302; 38607</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>840970; 1087759</t>
+          <t>713361; 763640</t>
         </is>
       </c>
     </row>
